--- a/AtchisonRegime/Outputs/USA/df_regCLI_USA.xlsx
+++ b/AtchisonRegime/Outputs/USA/df_regCLI_USA.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H809"/>
+  <dimension ref="A1:H810"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21203,22 +21203,22 @@
         <v>45443</v>
       </c>
       <c r="B799" t="n">
-        <v>99.72</v>
+        <v>99.69945</v>
       </c>
       <c r="C799" t="n">
-        <v>99.69375333333333</v>
+        <v>99.68690333333332</v>
       </c>
       <c r="D799" t="n">
-        <v>99.71485416666667</v>
+        <v>99.71428333333333</v>
       </c>
       <c r="E799" t="n">
-        <v>0.935149280750422</v>
+        <v>0.9351523219425059</v>
       </c>
       <c r="F799" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G799" t="n">
-        <v>0.006266379198084816</v>
+        <v>-0.01570867082860625</v>
       </c>
       <c r="H799" t="b">
         <v>1</v>
@@ -21229,22 +21229,22 @@
         <v>45473</v>
       </c>
       <c r="B800" t="n">
-        <v>99.73999999999999</v>
+        <v>99.70403</v>
       </c>
       <c r="C800" t="n">
-        <v>99.72471333333333</v>
+        <v>99.70587333333333</v>
       </c>
       <c r="D800" t="n">
-        <v>99.67033194444444</v>
+        <v>99.66876194444444</v>
       </c>
       <c r="E800" t="n">
-        <v>0.8926159094637026</v>
+        <v>0.8925290678574962</v>
       </c>
       <c r="F800" t="b">
         <v>1</v>
       </c>
       <c r="G800" t="n">
-        <v>0.02240605369896704</v>
+        <v>0.005131485533573125</v>
       </c>
       <c r="H800" t="b">
         <v>1</v>
@@ -21255,22 +21255,22 @@
         <v>45504</v>
       </c>
       <c r="B801" t="n">
-        <v>99.79000000000001</v>
+        <v>99.74187000000001</v>
       </c>
       <c r="C801" t="n">
-        <v>99.75</v>
+        <v>99.71511666666667</v>
       </c>
       <c r="D801" t="n">
-        <v>99.62866527777777</v>
+        <v>99.62575833333334</v>
       </c>
       <c r="E801" t="n">
-        <v>0.8487841135126887</v>
+        <v>0.8483874042391257</v>
       </c>
       <c r="F801" t="b">
         <v>1</v>
       </c>
       <c r="G801" t="n">
-        <v>0.05890779434252914</v>
+        <v>0.04460226520446691</v>
       </c>
       <c r="H801" t="b">
         <v>1</v>
@@ -21281,22 +21281,22 @@
         <v>45535</v>
       </c>
       <c r="B802" t="n">
-        <v>99.90000000000001</v>
+        <v>99.82787</v>
       </c>
       <c r="C802" t="n">
-        <v>99.81</v>
+        <v>99.75792333333334</v>
       </c>
       <c r="D802" t="n">
-        <v>99.59207916666668</v>
+        <v>99.58716861111112</v>
       </c>
       <c r="E802" t="n">
-        <v>0.8056499877220874</v>
+        <v>0.8043899621885001</v>
       </c>
       <c r="F802" t="b">
         <v>1</v>
       </c>
       <c r="G802" t="n">
-        <v>0.1365357185829741</v>
+        <v>0.10691331821946</v>
       </c>
       <c r="H802" t="b">
         <v>1</v>
@@ -21307,22 +21307,22 @@
         <v>45565</v>
       </c>
       <c r="B803" t="n">
-        <v>100.05</v>
+        <v>99.96052</v>
       </c>
       <c r="C803" t="n">
-        <v>99.91333333333334</v>
+        <v>99.84341999999999</v>
       </c>
       <c r="D803" t="n">
-        <v>99.56132638888889</v>
+        <v>99.55393027777777</v>
       </c>
       <c r="E803" t="n">
-        <v>0.7642712958037972</v>
+        <v>0.761229208269723</v>
       </c>
       <c r="F803" t="b">
         <v>1</v>
       </c>
       <c r="G803" t="n">
-        <v>0.19626538484902</v>
+        <v>0.1742576329953394</v>
       </c>
       <c r="H803" t="b">
         <v>1</v>
@@ -21333,22 +21333,22 @@
         <v>45596</v>
       </c>
       <c r="B804" t="n">
-        <v>100.23</v>
+        <v>100.1211</v>
       </c>
       <c r="C804" t="n">
-        <v>100.06</v>
+        <v>99.96983</v>
       </c>
       <c r="D804" t="n">
-        <v>99.5367013888889</v>
+        <v>99.52628027777779</v>
       </c>
       <c r="E804" t="n">
-        <v>0.7260578656718076</v>
+        <v>0.7198011890257949</v>
       </c>
       <c r="F804" t="b">
         <v>1</v>
       </c>
       <c r="G804" t="n">
-        <v>0.2479141243562677</v>
+        <v>0.2230893786343014</v>
       </c>
       <c r="H804" t="b">
         <v>1</v>
@@ -21359,22 +21359,22 @@
         <v>45626</v>
       </c>
       <c r="B805" t="n">
-        <v>100.41</v>
+        <v>100.2861</v>
       </c>
       <c r="C805" t="n">
-        <v>100.23</v>
+        <v>100.1225733333333</v>
       </c>
       <c r="D805" t="n">
-        <v>99.51801805555556</v>
+        <v>99.50415527777778</v>
       </c>
       <c r="E805" t="n">
-        <v>0.6930446777799673</v>
+        <v>0.6818368820494737</v>
       </c>
       <c r="F805" t="b">
         <v>1</v>
       </c>
       <c r="G805" t="n">
-        <v>0.2597235153389927</v>
+        <v>0.2419933628466199</v>
       </c>
       <c r="H805" t="b">
         <v>1</v>
@@ -21385,22 +21385,22 @@
         <v>45657</v>
       </c>
       <c r="B806" t="n">
-        <v>100.55</v>
+        <v>100.4219</v>
       </c>
       <c r="C806" t="n">
-        <v>100.3966666666667</v>
+        <v>100.2763666666667</v>
       </c>
       <c r="D806" t="n">
-        <v>99.50469027777778</v>
+        <v>99.48726916666666</v>
       </c>
       <c r="E806" t="n">
-        <v>0.6672756938756528</v>
+        <v>0.6497461519719171</v>
       </c>
       <c r="F806" t="b">
         <v>1</v>
       </c>
       <c r="G806" t="n">
-        <v>0.2098083315261438</v>
+        <v>0.2090047006632499</v>
       </c>
       <c r="H806" t="b">
         <v>1</v>
@@ -21411,22 +21411,22 @@
         <v>45688</v>
       </c>
       <c r="B807" t="n">
-        <v>100.65</v>
+        <v>100.5018</v>
       </c>
       <c r="C807" t="n">
-        <v>100.5366666666667</v>
+        <v>100.4032666666667</v>
       </c>
       <c r="D807" t="n">
-        <v>99.49662083333334</v>
+        <v>99.47508305555556</v>
       </c>
       <c r="E807" t="n">
-        <v>0.6509735661756599</v>
+        <v>0.6253684417998233</v>
       </c>
       <c r="F807" t="b">
         <v>1</v>
       </c>
       <c r="G807" t="n">
-        <v>0.1536160686024298</v>
+        <v>0.1277646818410845</v>
       </c>
       <c r="H807" t="b">
         <v>1</v>
@@ -21437,22 +21437,22 @@
         <v>45716</v>
       </c>
       <c r="B808" t="n">
-        <v>100.68</v>
+        <v>100.5202</v>
       </c>
       <c r="C808" t="n">
-        <v>100.6266666666667</v>
+        <v>100.4813</v>
       </c>
       <c r="D808" t="n">
-        <v>99.49314305555555</v>
+        <v>99.46716638888888</v>
       </c>
       <c r="E808" t="n">
-        <v>0.6440807809577453</v>
+        <v>0.6096556679596524</v>
       </c>
       <c r="F808" t="b">
         <v>1</v>
       </c>
       <c r="G808" t="n">
-        <v>0.04657800836005581</v>
+        <v>0.03018097094312175</v>
       </c>
       <c r="H808" t="b">
         <v>1</v>
@@ -21463,24 +21463,50 @@
         <v>45747</v>
       </c>
       <c r="B809" t="n">
-        <v>100.68</v>
+        <v>100.4902</v>
       </c>
       <c r="C809" t="n">
-        <v>100.67</v>
+        <v>100.5040666666667</v>
       </c>
       <c r="D809" t="n">
-        <v>99.49514305555556</v>
+        <v>99.46389416666666</v>
       </c>
       <c r="E809" t="n">
-        <v>0.6477429215353414</v>
+        <v>0.6036439855477963</v>
       </c>
       <c r="F809" t="b">
         <v>0</v>
       </c>
       <c r="G809" t="n">
-        <v>0</v>
+        <v>-0.04969816765883398</v>
       </c>
       <c r="H809" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B810" t="n">
+        <v>100.4417</v>
+      </c>
+      <c r="C810" t="n">
+        <v>100.4840333333333</v>
+      </c>
+      <c r="D810" t="n">
+        <v>99.46648305555556</v>
+      </c>
+      <c r="E810" t="n">
+        <v>0.6077322631358995</v>
+      </c>
+      <c r="F810" t="b">
+        <v>0</v>
+      </c>
+      <c r="G810" t="n">
+        <v>-0.07980487945422567</v>
+      </c>
+      <c r="H810" t="b">
         <v>1</v>
       </c>
     </row>

--- a/AtchisonRegime/Outputs/USA/df_regCLI_USA.xlsx
+++ b/AtchisonRegime/Outputs/USA/df_regCLI_USA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H810"/>
+  <dimension ref="A1:H811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21229,22 +21229,22 @@
         <v>45473</v>
       </c>
       <c r="B800" t="n">
-        <v>99.70403</v>
+        <v>99.75503999999999</v>
       </c>
       <c r="C800" t="n">
-        <v>99.70587333333333</v>
+        <v>99.72287666666666</v>
       </c>
       <c r="D800" t="n">
-        <v>99.66876194444444</v>
+        <v>99.67017888888888</v>
       </c>
       <c r="E800" t="n">
-        <v>0.8925290678574962</v>
+        <v>0.892627143128828</v>
       </c>
       <c r="F800" t="b">
         <v>1</v>
       </c>
       <c r="G800" t="n">
-        <v>0.005131485533573125</v>
+        <v>0.06227684249567139</v>
       </c>
       <c r="H800" t="b">
         <v>1</v>
@@ -21255,22 +21255,22 @@
         <v>45504</v>
       </c>
       <c r="B801" t="n">
-        <v>99.74187000000001</v>
+        <v>99.79371999999999</v>
       </c>
       <c r="C801" t="n">
-        <v>99.71511666666667</v>
+        <v>99.74940333333332</v>
       </c>
       <c r="D801" t="n">
-        <v>99.62575833333334</v>
+        <v>99.62861555555556</v>
       </c>
       <c r="E801" t="n">
-        <v>0.8483874042391257</v>
+        <v>0.848808646995388</v>
       </c>
       <c r="F801" t="b">
         <v>1</v>
       </c>
       <c r="G801" t="n">
-        <v>0.04460226520446691</v>
+        <v>0.04556975254307176</v>
       </c>
       <c r="H801" t="b">
         <v>1</v>
@@ -21281,22 +21281,22 @@
         <v>45535</v>
       </c>
       <c r="B802" t="n">
-        <v>99.82787</v>
+        <v>99.87848</v>
       </c>
       <c r="C802" t="n">
-        <v>99.75792333333334</v>
+        <v>99.80907999999999</v>
       </c>
       <c r="D802" t="n">
-        <v>99.58716861111112</v>
+        <v>99.59143166666667</v>
       </c>
       <c r="E802" t="n">
-        <v>0.8043899621885001</v>
+        <v>0.8054464331839474</v>
       </c>
       <c r="F802" t="b">
         <v>1</v>
       </c>
       <c r="G802" t="n">
-        <v>0.10691331821946</v>
+        <v>0.1052335655208562</v>
       </c>
       <c r="H802" t="b">
         <v>1</v>
@@ -21307,22 +21307,22 @@
         <v>45565</v>
       </c>
       <c r="B803" t="n">
-        <v>99.96052</v>
+        <v>100.0104</v>
       </c>
       <c r="C803" t="n">
-        <v>99.84341999999999</v>
+        <v>99.8942</v>
       </c>
       <c r="D803" t="n">
-        <v>99.55393027777777</v>
+        <v>99.55957888888889</v>
       </c>
       <c r="E803" t="n">
-        <v>0.761229208269723</v>
+        <v>0.7633334796341172</v>
       </c>
       <c r="F803" t="b">
         <v>1</v>
       </c>
       <c r="G803" t="n">
-        <v>0.1742576329953394</v>
+        <v>0.1728209275757697</v>
       </c>
       <c r="H803" t="b">
         <v>1</v>
@@ -21333,22 +21333,22 @@
         <v>45596</v>
       </c>
       <c r="B804" t="n">
-        <v>100.1211</v>
+        <v>100.1684</v>
       </c>
       <c r="C804" t="n">
-        <v>99.96983</v>
+        <v>100.0190933333333</v>
       </c>
       <c r="D804" t="n">
-        <v>99.52628027777779</v>
+        <v>99.53324277777779</v>
       </c>
       <c r="E804" t="n">
-        <v>0.7198011890257949</v>
+        <v>0.723393206092513</v>
       </c>
       <c r="F804" t="b">
         <v>1</v>
       </c>
       <c r="G804" t="n">
-        <v>0.2230893786343014</v>
+        <v>0.2184151007630489</v>
       </c>
       <c r="H804" t="b">
         <v>1</v>
@@ -21359,22 +21359,22 @@
         <v>45626</v>
       </c>
       <c r="B805" t="n">
-        <v>100.2861</v>
+        <v>100.3267</v>
       </c>
       <c r="C805" t="n">
-        <v>100.1225733333333</v>
+        <v>100.1685</v>
       </c>
       <c r="D805" t="n">
-        <v>99.50415527777778</v>
+        <v>99.51224555555557</v>
       </c>
       <c r="E805" t="n">
-        <v>0.6818368820494737</v>
+        <v>0.687201682454593</v>
       </c>
       <c r="F805" t="b">
         <v>1</v>
       </c>
       <c r="G805" t="n">
-        <v>0.2419933628466199</v>
+        <v>0.2303545000567671</v>
       </c>
       <c r="H805" t="b">
         <v>1</v>
@@ -21385,22 +21385,22 @@
         <v>45657</v>
       </c>
       <c r="B806" t="n">
-        <v>100.4219</v>
+        <v>100.4472</v>
       </c>
       <c r="C806" t="n">
-        <v>100.2763666666667</v>
+        <v>100.3141</v>
       </c>
       <c r="D806" t="n">
-        <v>99.48726916666666</v>
+        <v>99.49606222222221</v>
       </c>
       <c r="E806" t="n">
-        <v>0.6497461519719171</v>
+        <v>0.6566224234504535</v>
       </c>
       <c r="F806" t="b">
         <v>1</v>
       </c>
       <c r="G806" t="n">
-        <v>0.2090047006632499</v>
+        <v>0.1835149024713215</v>
       </c>
       <c r="H806" t="b">
         <v>1</v>
@@ -21411,22 +21411,22 @@
         <v>45688</v>
       </c>
       <c r="B807" t="n">
-        <v>100.5018</v>
+        <v>100.4989</v>
       </c>
       <c r="C807" t="n">
-        <v>100.4032666666667</v>
+        <v>100.4242666666667</v>
       </c>
       <c r="D807" t="n">
-        <v>99.47508305555556</v>
+        <v>99.48379555555556</v>
       </c>
       <c r="E807" t="n">
-        <v>0.6253684417998233</v>
+        <v>0.6325508765285162</v>
       </c>
       <c r="F807" t="b">
         <v>1</v>
       </c>
       <c r="G807" t="n">
-        <v>0.1277646818410845</v>
+        <v>0.08173255609690118</v>
       </c>
       <c r="H807" t="b">
         <v>1</v>
@@ -21437,22 +21437,22 @@
         <v>45716</v>
       </c>
       <c r="B808" t="n">
-        <v>100.5202</v>
+        <v>100.4812</v>
       </c>
       <c r="C808" t="n">
-        <v>100.4813</v>
+        <v>100.4757666666667</v>
       </c>
       <c r="D808" t="n">
-        <v>99.46716638888888</v>
+        <v>99.47479555555554</v>
       </c>
       <c r="E808" t="n">
-        <v>0.6096556679596524</v>
+        <v>0.6152818475856593</v>
       </c>
       <c r="F808" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G808" t="n">
-        <v>0.03018097094312175</v>
+        <v>-0.0287673040728554</v>
       </c>
       <c r="H808" t="b">
         <v>1</v>
@@ -21463,22 +21463,22 @@
         <v>45747</v>
       </c>
       <c r="B809" t="n">
-        <v>100.4902</v>
+        <v>100.4127</v>
       </c>
       <c r="C809" t="n">
-        <v>100.5040666666667</v>
+        <v>100.4642666666667</v>
       </c>
       <c r="D809" t="n">
-        <v>99.46389416666666</v>
+        <v>99.46937055555556</v>
       </c>
       <c r="E809" t="n">
-        <v>0.6036439855477963</v>
+        <v>0.6057926153960794</v>
       </c>
       <c r="F809" t="b">
         <v>0</v>
       </c>
       <c r="G809" t="n">
-        <v>-0.04969816765883398</v>
+        <v>-0.1130750000232564</v>
       </c>
       <c r="H809" t="b">
         <v>1</v>
@@ -21489,28 +21489,341 @@
         <v>45777</v>
       </c>
       <c r="B810" t="n">
-        <v>100.4417</v>
+        <v>100.3328</v>
       </c>
       <c r="C810" t="n">
-        <v>100.4840333333333</v>
+        <v>100.4089</v>
       </c>
       <c r="D810" t="n">
-        <v>99.46648305555556</v>
+        <v>99.46893444444444</v>
       </c>
       <c r="E810" t="n">
-        <v>0.6077322631358995</v>
+        <v>0.6051469533190094</v>
       </c>
       <c r="F810" t="b">
         <v>0</v>
       </c>
       <c r="G810" t="n">
-        <v>-0.07980487945422567</v>
+        <v>-0.1320340448907042</v>
       </c>
       <c r="H810" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="2" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B811" t="n">
+        <v>100.2888</v>
+      </c>
+      <c r="C811" t="n">
+        <v>100.3447666666667</v>
+      </c>
+      <c r="D811" t="n">
+        <v>99.47602055555555</v>
+      </c>
+      <c r="E811" t="n">
+        <v>0.6133866400891453</v>
+      </c>
+      <c r="F811" t="b">
+        <v>0</v>
+      </c>
+      <c r="G811" t="n">
+        <v>-0.07173289590007452</v>
+      </c>
+      <c r="H811" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005C6577D0C3AE724BBB504F46D5A19401" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="17afb16e0fbe716d3dcf2481b32b5550">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="df76e320-99cb-4a11-b59f-8bf32867ab70" xmlns:ns3="c0789f30-979e-497b-8344-faefb3987540" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f6d0bb8d4e6a5d6b988ea2ed2503dbb5" ns2:_="" ns3:_="">
+    <xsd:import namespace="df76e320-99cb-4a11-b59f-8bf32867ab70"/>
+    <xsd:import namespace="c0789f30-979e-497b-8344-faefb3987540"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="df76e320-99cb-4a11-b59f-8bf32867ab70" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2ea5f6a7-5373-4784-9cd5-4ca8be386d98" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="23" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c0789f30-979e-497b-8344-faefb3987540" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="22" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{f1100522-260f-4f17-9a31-47a12622b1e0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="c0789f30-979e-497b-8344-faefb3987540">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c0789f30-979e-497b-8344-faefb3987540" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="df76e320-99cb-4a11-b59f-8bf32867ab70">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B08D929-BBEA-44C6-B2E3-572A6E08C48C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B818E5C-73BE-486E-991E-D4EC4E73789E}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557C700D-A616-41A5-9F44-B26D9E91F79B}"/>
 </file>
--- a/AtchisonRegime/Outputs/USA/df_regCLI_USA.xlsx
+++ b/AtchisonRegime/Outputs/USA/df_regCLI_USA.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H811"/>
+  <dimension ref="A1:H812"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21255,22 +21255,22 @@
         <v>45504</v>
       </c>
       <c r="B801" t="n">
-        <v>99.79371999999999</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="C801" t="n">
-        <v>99.74940333333332</v>
+        <v>99.72149666666667</v>
       </c>
       <c r="D801" t="n">
-        <v>99.62861555555556</v>
+        <v>99.62629</v>
       </c>
       <c r="E801" t="n">
-        <v>0.848808646995388</v>
+        <v>0.8484579866222193</v>
       </c>
       <c r="F801" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G801" t="n">
-        <v>0.04556975254307176</v>
+        <v>-0.05308453772626753</v>
       </c>
       <c r="H801" t="b">
         <v>1</v>
@@ -21281,22 +21281,22 @@
         <v>45535</v>
       </c>
       <c r="B802" t="n">
-        <v>99.87848</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="C802" t="n">
-        <v>99.80907999999999</v>
+        <v>99.75168000000001</v>
       </c>
       <c r="D802" t="n">
-        <v>99.59143166666667</v>
+        <v>99.58664833333334</v>
       </c>
       <c r="E802" t="n">
-        <v>0.8054464331839474</v>
+        <v>0.8041923244154615</v>
       </c>
       <c r="F802" t="b">
         <v>1</v>
       </c>
       <c r="G802" t="n">
-        <v>0.1052335655208562</v>
+        <v>0.0994786913169827</v>
       </c>
       <c r="H802" t="b">
         <v>1</v>
@@ -21307,22 +21307,22 @@
         <v>45565</v>
       </c>
       <c r="B803" t="n">
-        <v>100.0104</v>
+        <v>99.91</v>
       </c>
       <c r="C803" t="n">
-        <v>99.8942</v>
+        <v>99.80333333333333</v>
       </c>
       <c r="D803" t="n">
-        <v>99.55957888888889</v>
+        <v>99.55200666666666</v>
       </c>
       <c r="E803" t="n">
-        <v>0.7633334796341172</v>
+        <v>0.7602710334987866</v>
       </c>
       <c r="F803" t="b">
         <v>1</v>
       </c>
       <c r="G803" t="n">
-        <v>0.1728209275757697</v>
+        <v>0.1578384480173436</v>
       </c>
       <c r="H803" t="b">
         <v>1</v>
@@ -21333,22 +21333,22 @@
         <v>45596</v>
       </c>
       <c r="B804" t="n">
-        <v>100.1684</v>
+        <v>100.05</v>
       </c>
       <c r="C804" t="n">
-        <v>100.0190933333333</v>
+        <v>99.91666666666667</v>
       </c>
       <c r="D804" t="n">
-        <v>99.53324277777779</v>
+        <v>99.52238166666667</v>
       </c>
       <c r="E804" t="n">
-        <v>0.723393206092513</v>
+        <v>0.7171209194850102</v>
       </c>
       <c r="F804" t="b">
         <v>1</v>
       </c>
       <c r="G804" t="n">
-        <v>0.2184151007630489</v>
+        <v>0.1952250955118413</v>
       </c>
       <c r="H804" t="b">
         <v>1</v>
@@ -21359,22 +21359,22 @@
         <v>45626</v>
       </c>
       <c r="B805" t="n">
-        <v>100.3267</v>
+        <v>100.2</v>
       </c>
       <c r="C805" t="n">
-        <v>100.1685</v>
+        <v>100.0533333333333</v>
       </c>
       <c r="D805" t="n">
-        <v>99.51224555555557</v>
+        <v>99.49786499999999</v>
       </c>
       <c r="E805" t="n">
-        <v>0.687201682454593</v>
+        <v>0.6761747747165864</v>
       </c>
       <c r="F805" t="b">
         <v>1</v>
       </c>
       <c r="G805" t="n">
-        <v>0.2303545000567671</v>
+        <v>0.2218361370592049</v>
       </c>
       <c r="H805" t="b">
         <v>1</v>
@@ -21385,22 +21385,22 @@
         <v>45657</v>
       </c>
       <c r="B806" t="n">
-        <v>100.4472</v>
+        <v>100.31</v>
       </c>
       <c r="C806" t="n">
-        <v>100.3141</v>
+        <v>100.1866666666667</v>
       </c>
       <c r="D806" t="n">
-        <v>99.49606222222221</v>
+        <v>99.47787055555554</v>
       </c>
       <c r="E806" t="n">
-        <v>0.6566224234504535</v>
+        <v>0.6392133071561997</v>
       </c>
       <c r="F806" t="b">
         <v>1</v>
       </c>
       <c r="G806" t="n">
-        <v>0.1835149024713215</v>
+        <v>0.1720865300651815</v>
       </c>
       <c r="H806" t="b">
         <v>1</v>
@@ -21411,22 +21411,22 @@
         <v>45688</v>
       </c>
       <c r="B807" t="n">
-        <v>100.4989</v>
+        <v>100.36</v>
       </c>
       <c r="C807" t="n">
-        <v>100.4242666666667</v>
+        <v>100.29</v>
       </c>
       <c r="D807" t="n">
-        <v>99.48379555555556</v>
+        <v>99.46174555555555</v>
       </c>
       <c r="E807" t="n">
-        <v>0.6325508765285162</v>
+        <v>0.6078130521819261</v>
       </c>
       <c r="F807" t="b">
         <v>1</v>
       </c>
       <c r="G807" t="n">
-        <v>0.08173255609690118</v>
+        <v>0.08226213606388882</v>
       </c>
       <c r="H807" t="b">
         <v>1</v>
@@ -21437,22 +21437,22 @@
         <v>45716</v>
       </c>
       <c r="B808" t="n">
-        <v>100.4812</v>
+        <v>100.35</v>
       </c>
       <c r="C808" t="n">
-        <v>100.4757666666667</v>
+        <v>100.34</v>
       </c>
       <c r="D808" t="n">
-        <v>99.47479555555554</v>
+        <v>99.4491011111111</v>
       </c>
       <c r="E808" t="n">
-        <v>0.6152818475856593</v>
+        <v>0.5833071988182426</v>
       </c>
       <c r="F808" t="b">
         <v>0</v>
       </c>
       <c r="G808" t="n">
-        <v>-0.0287673040728554</v>
+        <v>-0.01714362521200617</v>
       </c>
       <c r="H808" t="b">
         <v>1</v>
@@ -21463,22 +21463,22 @@
         <v>45747</v>
       </c>
       <c r="B809" t="n">
-        <v>100.4127</v>
+        <v>100.32</v>
       </c>
       <c r="C809" t="n">
-        <v>100.4642666666667</v>
+        <v>100.3433333333333</v>
       </c>
       <c r="D809" t="n">
-        <v>99.46937055555556</v>
+        <v>99.44110111111111</v>
       </c>
       <c r="E809" t="n">
-        <v>0.6057926153960794</v>
+        <v>0.5687522515311528</v>
       </c>
       <c r="F809" t="b">
         <v>0</v>
       </c>
       <c r="G809" t="n">
-        <v>-0.1130750000232564</v>
+        <v>-0.05274704393562812</v>
       </c>
       <c r="H809" t="b">
         <v>1</v>
@@ -21489,22 +21489,22 @@
         <v>45777</v>
       </c>
       <c r="B810" t="n">
-        <v>100.3328</v>
+        <v>100.3</v>
       </c>
       <c r="C810" t="n">
-        <v>100.4089</v>
+        <v>100.3233333333333</v>
       </c>
       <c r="D810" t="n">
-        <v>99.46893444444444</v>
+        <v>99.4397538888889</v>
       </c>
       <c r="E810" t="n">
-        <v>0.6051469533190094</v>
+        <v>0.5665948046824858</v>
       </c>
       <c r="F810" t="b">
         <v>0</v>
       </c>
       <c r="G810" t="n">
-        <v>-0.1320340448907042</v>
+        <v>-0.0352985940476525</v>
       </c>
       <c r="H810" t="b">
         <v>0</v>
@@ -21515,24 +21515,50 @@
         <v>45808</v>
       </c>
       <c r="B811" t="n">
-        <v>100.2888</v>
+        <v>100.34</v>
       </c>
       <c r="C811" t="n">
-        <v>100.3447666666667</v>
+        <v>100.32</v>
       </c>
       <c r="D811" t="n">
-        <v>99.47602055555555</v>
+        <v>99.44826222222223</v>
       </c>
       <c r="E811" t="n">
-        <v>0.6133866400891453</v>
+        <v>0.5779546081886688</v>
       </c>
       <c r="F811" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>-0.07173289590007452</v>
+        <v>0.0692095874542254</v>
       </c>
       <c r="H811" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B812" t="n">
+        <v>100.43</v>
+      </c>
+      <c r="C812" t="n">
+        <v>100.3566666666667</v>
+      </c>
+      <c r="D812" t="n">
+        <v>99.4682363888889</v>
+      </c>
+      <c r="E812" t="n">
+        <v>0.5993223649193058</v>
+      </c>
+      <c r="F812" t="b">
+        <v>1</v>
+      </c>
+      <c r="G812" t="n">
+        <v>0.1501696003153849</v>
+      </c>
+      <c r="H812" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21817,13 +21843,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B08D929-BBEA-44C6-B2E3-572A6E08C48C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7463FAFB-69D2-4112-A1A5-D0AD0D396870}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B818E5C-73BE-486E-991E-D4EC4E73789E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F32E9D1F-3238-431A-AB5A-43F06CAB9483}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557C700D-A616-41A5-9F44-B26D9E91F79B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4638680-E3D2-4C7A-8B9D-AB302F98F1EB}"/>
 </file>
--- a/AtchisonRegime/Outputs/USA/df_regCLI_USA.xlsx
+++ b/AtchisonRegime/Outputs/USA/df_regCLI_USA.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H812"/>
+  <dimension ref="A1:H815"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21281,22 +21281,22 @@
         <v>45535</v>
       </c>
       <c r="B802" t="n">
-        <v>99.79000000000001</v>
+        <v>99.7561</v>
       </c>
       <c r="C802" t="n">
-        <v>99.75168000000001</v>
+        <v>99.74038</v>
       </c>
       <c r="D802" t="n">
-        <v>99.58664833333334</v>
+        <v>99.58570666666668</v>
       </c>
       <c r="E802" t="n">
-        <v>0.8041923244154615</v>
+        <v>0.8039672231628422</v>
       </c>
       <c r="F802" t="b">
         <v>1</v>
       </c>
       <c r="G802" t="n">
-        <v>0.0994786913169827</v>
+        <v>0.05734064607590641</v>
       </c>
       <c r="H802" t="b">
         <v>1</v>
@@ -21307,22 +21307,22 @@
         <v>45565</v>
       </c>
       <c r="B803" t="n">
-        <v>99.91</v>
+        <v>99.85778000000001</v>
       </c>
       <c r="C803" t="n">
-        <v>99.80333333333333</v>
+        <v>99.77462666666666</v>
       </c>
       <c r="D803" t="n">
-        <v>99.55200666666666</v>
+        <v>99.54961444444444</v>
       </c>
       <c r="E803" t="n">
-        <v>0.7602710334987866</v>
+        <v>0.7593336722171025</v>
       </c>
       <c r="F803" t="b">
         <v>1</v>
       </c>
       <c r="G803" t="n">
-        <v>0.1578384480173436</v>
+        <v>0.1339068761472364</v>
       </c>
       <c r="H803" t="b">
         <v>1</v>
@@ -21333,22 +21333,22 @@
         <v>45596</v>
       </c>
       <c r="B804" t="n">
-        <v>100.05</v>
+        <v>100.004</v>
       </c>
       <c r="C804" t="n">
-        <v>99.91666666666667</v>
+        <v>99.87262666666668</v>
       </c>
       <c r="D804" t="n">
-        <v>99.52238166666667</v>
+        <v>99.51871166666666</v>
       </c>
       <c r="E804" t="n">
-        <v>0.7171209194850102</v>
+        <v>0.7150928700986212</v>
       </c>
       <c r="F804" t="b">
         <v>1</v>
       </c>
       <c r="G804" t="n">
-        <v>0.1952250955118413</v>
+        <v>0.2044769373519747</v>
       </c>
       <c r="H804" t="b">
         <v>1</v>
@@ -21359,22 +21359,22 @@
         <v>45626</v>
       </c>
       <c r="B805" t="n">
-        <v>100.2</v>
+        <v>100.1511</v>
       </c>
       <c r="C805" t="n">
-        <v>100.0533333333333</v>
+        <v>100.0042933333333</v>
       </c>
       <c r="D805" t="n">
-        <v>99.49786499999999</v>
+        <v>99.49283666666666</v>
       </c>
       <c r="E805" t="n">
-        <v>0.6761747747165864</v>
+        <v>0.6724706934199732</v>
       </c>
       <c r="F805" t="b">
         <v>1</v>
       </c>
       <c r="G805" t="n">
-        <v>0.2218361370592049</v>
+        <v>0.2187455920969442</v>
       </c>
       <c r="H805" t="b">
         <v>1</v>
@@ -21385,22 +21385,22 @@
         <v>45657</v>
       </c>
       <c r="B806" t="n">
-        <v>100.31</v>
+        <v>100.2631</v>
       </c>
       <c r="C806" t="n">
-        <v>100.1866666666667</v>
+        <v>100.1394</v>
       </c>
       <c r="D806" t="n">
-        <v>99.47787055555554</v>
+        <v>99.47153944444443</v>
       </c>
       <c r="E806" t="n">
-        <v>0.6392133071561997</v>
+        <v>0.633410494459382</v>
       </c>
       <c r="F806" t="b">
         <v>1</v>
       </c>
       <c r="G806" t="n">
-        <v>0.1720865300651815</v>
+        <v>0.1768205626204333</v>
       </c>
       <c r="H806" t="b">
         <v>1</v>
@@ -21411,22 +21411,22 @@
         <v>45688</v>
       </c>
       <c r="B807" t="n">
-        <v>100.36</v>
+        <v>100.3115</v>
       </c>
       <c r="C807" t="n">
-        <v>100.29</v>
+        <v>100.2419</v>
       </c>
       <c r="D807" t="n">
-        <v>99.46174555555555</v>
+        <v>99.45406722222222</v>
       </c>
       <c r="E807" t="n">
-        <v>0.6078130521819261</v>
+        <v>0.5994999940552378</v>
       </c>
       <c r="F807" t="b">
         <v>1</v>
       </c>
       <c r="G807" t="n">
-        <v>0.08226213606388882</v>
+        <v>0.08073394575470391</v>
       </c>
       <c r="H807" t="b">
         <v>1</v>
@@ -21437,22 +21437,22 @@
         <v>45716</v>
       </c>
       <c r="B808" t="n">
-        <v>100.35</v>
+        <v>100.2993</v>
       </c>
       <c r="C808" t="n">
-        <v>100.34</v>
+        <v>100.2913</v>
       </c>
       <c r="D808" t="n">
-        <v>99.4491011111111</v>
+        <v>99.44001444444444</v>
       </c>
       <c r="E808" t="n">
-        <v>0.5833071988182426</v>
+        <v>0.5722326666087267</v>
       </c>
       <c r="F808" t="b">
         <v>0</v>
       </c>
       <c r="G808" t="n">
-        <v>-0.01714362521200617</v>
+        <v>-0.02131999920992771</v>
       </c>
       <c r="H808" t="b">
         <v>1</v>
@@ -21463,22 +21463,22 @@
         <v>45747</v>
       </c>
       <c r="B809" t="n">
-        <v>100.32</v>
+        <v>100.2487</v>
       </c>
       <c r="C809" t="n">
-        <v>100.3433333333333</v>
+        <v>100.2865</v>
       </c>
       <c r="D809" t="n">
-        <v>99.44110111111111</v>
+        <v>99.43003388888889</v>
       </c>
       <c r="E809" t="n">
-        <v>0.5687522515311528</v>
+        <v>0.554126182686665</v>
       </c>
       <c r="F809" t="b">
         <v>0</v>
       </c>
       <c r="G809" t="n">
-        <v>-0.05274704393562812</v>
+        <v>-0.09131494158003906</v>
       </c>
       <c r="H809" t="b">
         <v>1</v>
@@ -21489,22 +21489,22 @@
         <v>45777</v>
       </c>
       <c r="B810" t="n">
-        <v>100.3</v>
+        <v>100.2014</v>
       </c>
       <c r="C810" t="n">
-        <v>100.3233333333333</v>
+        <v>100.2498</v>
       </c>
       <c r="D810" t="n">
-        <v>99.4397538888889</v>
+        <v>99.42594777777778</v>
       </c>
       <c r="E810" t="n">
-        <v>0.5665948046824858</v>
+        <v>0.5476646141318868</v>
       </c>
       <c r="F810" t="b">
         <v>0</v>
       </c>
       <c r="G810" t="n">
-        <v>-0.0352985940476525</v>
+        <v>-0.08636672660505716</v>
       </c>
       <c r="H810" t="b">
         <v>0</v>
@@ -21515,22 +21515,22 @@
         <v>45808</v>
       </c>
       <c r="B811" t="n">
-        <v>100.34</v>
+        <v>100.2038</v>
       </c>
       <c r="C811" t="n">
-        <v>100.32</v>
+        <v>100.2179666666667</v>
       </c>
       <c r="D811" t="n">
-        <v>99.44826222222223</v>
+        <v>99.43067277777779</v>
       </c>
       <c r="E811" t="n">
-        <v>0.5779546081886688</v>
+        <v>0.553757712065691</v>
       </c>
       <c r="F811" t="b">
         <v>1</v>
       </c>
       <c r="G811" t="n">
-        <v>0.0692095874542254</v>
+        <v>0.00433402541888157</v>
       </c>
       <c r="H811" t="b">
         <v>0</v>
@@ -21541,25 +21541,103 @@
         <v>45838</v>
       </c>
       <c r="B812" t="n">
-        <v>100.43</v>
+        <v>100.2464</v>
       </c>
       <c r="C812" t="n">
-        <v>100.3566666666667</v>
+        <v>100.2172</v>
       </c>
       <c r="D812" t="n">
-        <v>99.4682363888889</v>
+        <v>99.44554694444444</v>
       </c>
       <c r="E812" t="n">
-        <v>0.5993223649193058</v>
+        <v>0.5684959667898066</v>
       </c>
       <c r="F812" t="b">
         <v>1</v>
       </c>
       <c r="G812" t="n">
-        <v>0.1501696003153849</v>
+        <v>0.07493456856087748</v>
       </c>
       <c r="H812" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B813" t="n">
+        <v>100.295</v>
+      </c>
+      <c r="C813" t="n">
+        <v>100.2484</v>
+      </c>
+      <c r="D813" t="n">
+        <v>99.46948111111112</v>
+      </c>
+      <c r="E813" t="n">
+        <v>0.5858417160331033</v>
+      </c>
+      <c r="F813" t="b">
+        <v>1</v>
+      </c>
+      <c r="G813" t="n">
+        <v>0.08295756118067453</v>
+      </c>
+      <c r="H813" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B814" t="n">
+        <v>100.3339</v>
+      </c>
+      <c r="C814" t="n">
+        <v>100.2917666666667</v>
+      </c>
+      <c r="D814" t="n">
+        <v>99.50048305555555</v>
+      </c>
+      <c r="E814" t="n">
+        <v>0.6014662907587889</v>
+      </c>
+      <c r="F814" t="b">
+        <v>1</v>
+      </c>
+      <c r="G814" t="n">
+        <v>0.0646752787274633</v>
+      </c>
+      <c r="H814" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B815" t="n">
+        <v>100.3687</v>
+      </c>
+      <c r="C815" t="n">
+        <v>100.3325333333333</v>
+      </c>
+      <c r="D815" t="n">
+        <v>99.53712444444444</v>
+      </c>
+      <c r="E815" t="n">
+        <v>0.6132778518023289</v>
+      </c>
+      <c r="F815" t="b">
+        <v>1</v>
+      </c>
+      <c r="G815" t="n">
+        <v>0.05674426346513629</v>
+      </c>
+      <c r="H815" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -21843,13 +21921,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7463FAFB-69D2-4112-A1A5-D0AD0D396870}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0E2F883-44B2-446F-9170-3FB071747E96}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F32E9D1F-3238-431A-AB5A-43F06CAB9483}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A40AD9B-005C-4083-B8C3-EBDD9330FDB2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4638680-E3D2-4C7A-8B9D-AB302F98F1EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE98EFAF-4296-425E-B28A-2E8F447A8C83}"/>
 </file>